--- a/00-esmagadora-modelo/dados_sujos/apontamentos_mensais/producao_2025_07.xlsx
+++ b/00-esmagadora-modelo/dados_sujos/apontamentos_mensais/producao_2025_07.xlsx
@@ -480,25 +480,25 @@
         <v>45839</v>
       </c>
       <c r="B5" t="n">
-        <v>745.6799999999999</v>
+        <v>1546.8</v>
       </c>
       <c r="C5" t="n">
-        <v>11.6</v>
+        <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>540.46</v>
+        <v>1122.11</v>
       </c>
       <c r="E5" t="n">
-        <v>148.07</v>
+        <v>303.6</v>
       </c>
       <c r="F5" t="n">
-        <v>1513</v>
+        <v>1402</v>
       </c>
       <c r="G5" t="n">
-        <v>195528</v>
+        <v>408422</v>
       </c>
       <c r="H5" t="n">
-        <v>33516</v>
+        <v>67640</v>
       </c>
     </row>
     <row r="6">
@@ -506,25 +506,25 @@
         <v>45840</v>
       </c>
       <c r="B6" t="n">
-        <v>564.04</v>
+        <v>1512.36</v>
       </c>
       <c r="C6" t="n">
-        <v>9.130000000000001</v>
+        <v>24</v>
       </c>
       <c r="D6" t="n">
-        <v>410.82</v>
+        <v>1097.55</v>
       </c>
       <c r="E6" t="n">
-        <v>110.47</v>
+        <v>302.07</v>
       </c>
       <c r="F6" t="n">
-        <v>977</v>
+        <v>1356</v>
       </c>
       <c r="G6" t="n">
-        <v>160395</v>
+        <v>406068</v>
       </c>
       <c r="H6" t="n">
-        <v>24614</v>
+        <v>71541</v>
       </c>
     </row>
     <row r="7">
@@ -532,25 +532,25 @@
         <v>45841</v>
       </c>
       <c r="B7" t="n">
-        <v>1139.34</v>
+        <v>1481.83</v>
       </c>
       <c r="C7" t="n">
-        <v>19.25</v>
+        <v>23.76</v>
       </c>
       <c r="D7" t="n">
-        <v>822.5</v>
+        <v>1073.53</v>
       </c>
       <c r="E7" t="n">
-        <v>236.13</v>
+        <v>304.75</v>
       </c>
       <c r="F7" t="n">
-        <v>1759</v>
+        <v>1195</v>
       </c>
       <c r="G7" t="n">
-        <v>320137</v>
+        <v>397165</v>
       </c>
       <c r="H7" t="n">
-        <v>50220</v>
+        <v>70286</v>
       </c>
     </row>
     <row r="8">
@@ -558,25 +558,25 @@
         <v>45842</v>
       </c>
       <c r="B8" t="n">
-        <v>557.42</v>
+        <v>1523.81</v>
       </c>
       <c r="C8" t="n">
-        <v>8.92</v>
+        <v>24</v>
       </c>
       <c r="D8" t="n">
-        <v>402.87</v>
+        <v>1111.17</v>
       </c>
       <c r="E8" t="n">
-        <v>111.17</v>
+        <v>311.94</v>
       </c>
       <c r="F8" t="n">
-        <v>959</v>
+        <v>1446</v>
       </c>
       <c r="G8" t="n">
-        <v>145785</v>
+        <v>418025</v>
       </c>
       <c r="H8" t="n">
-        <v>25175</v>
+        <v>68819</v>
       </c>
     </row>
     <row r="9">
@@ -584,25 +584,25 @@
         <v>45843</v>
       </c>
       <c r="B9" t="n">
-        <v>875.42</v>
+        <v>1372.55</v>
       </c>
       <c r="C9" t="n">
-        <v>14.21</v>
+        <v>22.41</v>
       </c>
       <c r="D9" t="n">
-        <v>634.4299999999999</v>
+        <v>994.74</v>
       </c>
       <c r="E9" t="n">
-        <v>169.92</v>
+        <v>264.67</v>
       </c>
       <c r="F9" t="n">
-        <v>2156</v>
+        <v>1333</v>
       </c>
       <c r="G9" t="n">
-        <v>255065</v>
+        <v>366586</v>
       </c>
       <c r="H9" t="n">
-        <v>39791</v>
+        <v>57918</v>
       </c>
     </row>
     <row r="10">
@@ -610,25 +610,25 @@
         <v>45844</v>
       </c>
       <c r="B10" t="n">
-        <v>825.8200000000001</v>
+        <v>1396.57</v>
       </c>
       <c r="C10" t="n">
-        <v>13.48</v>
+        <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>602.42</v>
+        <v>1014.2</v>
       </c>
       <c r="E10" t="n">
-        <v>165.35</v>
+        <v>280.11</v>
       </c>
       <c r="F10" t="n">
-        <v>1624</v>
+        <v>1229</v>
       </c>
       <c r="G10" t="n">
-        <v>218591</v>
+        <v>350668</v>
       </c>
       <c r="H10" t="n">
-        <v>36066</v>
+        <v>65678</v>
       </c>
     </row>
     <row r="11">
@@ -636,25 +636,25 @@
         <v>45845</v>
       </c>
       <c r="B11" t="n">
-        <v>1327.97</v>
+        <v>1467.92</v>
       </c>
       <c r="C11" t="n">
-        <v>21.12</v>
+        <v>24</v>
       </c>
       <c r="D11" t="n">
-        <v>965.29</v>
+        <v>1066.16</v>
       </c>
       <c r="E11" t="n">
-        <v>265.36</v>
+        <v>293.22</v>
       </c>
       <c r="F11" t="n">
-        <v>1793</v>
+        <v>1271</v>
       </c>
       <c r="G11" t="n">
-        <v>355441</v>
+        <v>394570</v>
       </c>
       <c r="H11" t="n">
-        <v>59491</v>
+        <v>66589</v>
       </c>
     </row>
     <row r="12">
@@ -662,25 +662,25 @@
         <v>45846</v>
       </c>
       <c r="B12" t="n">
-        <v>1432.29</v>
+        <v>1520.73</v>
       </c>
       <c r="C12" t="n">
-        <v>23.24</v>
+        <v>24</v>
       </c>
       <c r="D12" t="n">
-        <v>1033.11</v>
+        <v>1103.19</v>
       </c>
       <c r="E12" t="n">
-        <v>285.8</v>
+        <v>304.07</v>
       </c>
       <c r="F12" t="n">
-        <v>1983</v>
+        <v>1157</v>
       </c>
       <c r="G12" t="n">
-        <v>387676</v>
+        <v>381583</v>
       </c>
       <c r="H12" t="n">
-        <v>65562</v>
+        <v>67495</v>
       </c>
     </row>
     <row r="13">
@@ -688,25 +688,25 @@
         <v>45847</v>
       </c>
       <c r="B13" t="n">
-        <v>809.42</v>
+        <v>1444.53</v>
       </c>
       <c r="C13" t="n">
-        <v>13.19</v>
+        <v>23.01</v>
       </c>
       <c r="D13" t="n">
-        <v>587.14</v>
+        <v>1052.93</v>
       </c>
       <c r="E13" t="n">
-        <v>161.26</v>
+        <v>281.58</v>
       </c>
       <c r="F13" t="n">
-        <v>1488</v>
+        <v>1072</v>
       </c>
       <c r="G13" t="n">
-        <v>222496</v>
+        <v>373047</v>
       </c>
       <c r="H13" t="n">
-        <v>37590</v>
+        <v>65899</v>
       </c>
     </row>
     <row r="14">
@@ -714,25 +714,25 @@
         <v>45848</v>
       </c>
       <c r="B14" t="n">
-        <v>1531.8</v>
+        <v>1441.36</v>
       </c>
       <c r="C14" t="n">
         <v>24</v>
       </c>
       <c r="D14" t="n">
-        <v>1104.98</v>
+        <v>1042.4</v>
       </c>
       <c r="E14" t="n">
-        <v>299.93</v>
+        <v>293.62</v>
       </c>
       <c r="F14" t="n">
-        <v>2193</v>
+        <v>1421</v>
       </c>
       <c r="G14" t="n">
-        <v>369382</v>
+        <v>409746</v>
       </c>
       <c r="H14" t="n">
-        <v>68259</v>
+        <v>65398</v>
       </c>
     </row>
     <row r="15">
@@ -740,25 +740,25 @@
         <v>45849</v>
       </c>
       <c r="B15" t="n">
-        <v>1180.25</v>
+        <v>1232.29</v>
       </c>
       <c r="C15" t="n">
-        <v>18.73</v>
+        <v>20.31</v>
       </c>
       <c r="D15" t="n">
-        <v>854.79</v>
+        <v>899.27</v>
       </c>
       <c r="E15" t="n">
-        <v>233.48</v>
+        <v>243.75</v>
       </c>
       <c r="F15" t="n">
-        <v>2021</v>
+        <v>1122</v>
       </c>
       <c r="G15" t="n">
-        <v>339060</v>
+        <v>323698</v>
       </c>
       <c r="H15" t="n">
-        <v>53121</v>
+        <v>53262</v>
       </c>
     </row>
     <row r="16">
@@ -766,25 +766,25 @@
         <v>45850</v>
       </c>
       <c r="B16" t="n">
-        <v>1017.33</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>16.79</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>742.37</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>200.74</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1982</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>281806</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>45226</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -792,25 +792,25 @@
         <v>45851</v>
       </c>
       <c r="B17" t="n">
-        <v>560.46</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>405.66</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>112.63</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1024</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>153934</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>24999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -818,25 +818,25 @@
         <v>45852</v>
       </c>
       <c r="B18" t="n">
-        <v>1466.24</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>23.12</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1051.11</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>277.93</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>2219</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>416352</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>67386</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -844,25 +844,25 @@
         <v>45853</v>
       </c>
       <c r="B19" t="n">
-        <v>1529.29</v>
+        <v>1583.24</v>
       </c>
       <c r="C19" t="n">
         <v>24</v>
       </c>
       <c r="D19" t="n">
-        <v>1101.88</v>
+        <v>1146.11</v>
       </c>
       <c r="E19" t="n">
-        <v>309.43</v>
+        <v>312.84</v>
       </c>
       <c r="F19" t="n">
-        <v>2001</v>
+        <v>1349</v>
       </c>
       <c r="G19" t="n">
-        <v>393097</v>
+        <v>415493</v>
       </c>
       <c r="H19" t="n">
-        <v>69542</v>
+        <v>74200</v>
       </c>
     </row>
     <row r="20">
@@ -870,25 +870,25 @@
         <v>45854</v>
       </c>
       <c r="B20" t="n">
-        <v>1061.99</v>
+        <v>1391.88</v>
       </c>
       <c r="C20" t="n">
-        <v>17.52</v>
+        <v>24</v>
       </c>
       <c r="D20" t="n">
-        <v>774.86</v>
+        <v>1005.57</v>
       </c>
       <c r="E20" t="n">
-        <v>206.59</v>
+        <v>272.76</v>
       </c>
       <c r="F20" t="n">
-        <v>1840</v>
+        <v>1171</v>
       </c>
       <c r="G20" t="n">
-        <v>275175</v>
+        <v>406169</v>
       </c>
       <c r="H20" t="n">
-        <v>48474</v>
+        <v>65138</v>
       </c>
     </row>
     <row r="21">
@@ -896,25 +896,25 @@
         <v>45855</v>
       </c>
       <c r="B21" t="n">
-        <v>695.33</v>
+        <v>576.34</v>
       </c>
       <c r="C21" t="n">
-        <v>10.77</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>496.93</v>
+        <v>421.38</v>
       </c>
       <c r="E21" t="n">
-        <v>137.25</v>
+        <v>113.16</v>
       </c>
       <c r="F21" t="n">
-        <v>1217</v>
+        <v>698</v>
       </c>
       <c r="G21" t="n">
-        <v>197127</v>
+        <v>166979</v>
       </c>
       <c r="H21" t="n">
-        <v>33173</v>
+        <v>25243</v>
       </c>
     </row>
     <row r="22">
@@ -922,25 +922,25 @@
         <v>45856</v>
       </c>
       <c r="B22" t="n">
-        <v>1313.47</v>
+        <v>1486.02</v>
       </c>
       <c r="C22" t="n">
-        <v>22.11</v>
+        <v>24</v>
       </c>
       <c r="D22" t="n">
-        <v>941.8</v>
+        <v>1075.36</v>
       </c>
       <c r="E22" t="n">
-        <v>265.84</v>
+        <v>304.01</v>
       </c>
       <c r="F22" t="n">
-        <v>1783</v>
+        <v>1259</v>
       </c>
       <c r="G22" t="n">
-        <v>345700</v>
+        <v>421686</v>
       </c>
       <c r="H22" t="n">
-        <v>57610</v>
+        <v>69776</v>
       </c>
     </row>
     <row r="23">
@@ -948,25 +948,25 @@
         <v>45857</v>
       </c>
       <c r="B23" t="n">
-        <v>1068.94</v>
+        <v>1474.91</v>
       </c>
       <c r="C23" t="n">
-        <v>17.2</v>
+        <v>24</v>
       </c>
       <c r="D23" t="n">
-        <v>773.67</v>
+        <v>1065.46</v>
       </c>
       <c r="E23" t="n">
-        <v>213.9</v>
+        <v>283.22</v>
       </c>
       <c r="F23" t="n">
-        <v>1624</v>
+        <v>1409</v>
       </c>
       <c r="G23" t="n">
-        <v>283088</v>
+        <v>400097</v>
       </c>
       <c r="H23" t="n">
-        <v>51130</v>
+        <v>65191</v>
       </c>
     </row>
     <row r="24">
@@ -974,25 +974,25 @@
         <v>45858</v>
       </c>
       <c r="B24" t="n">
-        <v>730.28</v>
+        <v>1236.2</v>
       </c>
       <c r="C24" t="n">
-        <v>12.6</v>
+        <v>20.16</v>
       </c>
       <c r="D24" t="n">
-        <v>531.37</v>
+        <v>895.87</v>
       </c>
       <c r="E24" t="n">
-        <v>146.8</v>
+        <v>241.62</v>
       </c>
       <c r="F24" t="n">
-        <v>1234</v>
+        <v>1213</v>
       </c>
       <c r="G24" t="n">
-        <v>206634</v>
+        <v>307205</v>
       </c>
       <c r="H24" t="n">
-        <v>33384</v>
+        <v>59239</v>
       </c>
     </row>
     <row r="25">
@@ -1000,25 +1000,25 @@
         <v>45859</v>
       </c>
       <c r="B25" t="n">
-        <v>1096.02</v>
+        <v>1449.86</v>
       </c>
       <c r="C25" t="n">
-        <v>17.95</v>
+        <v>24</v>
       </c>
       <c r="D25" t="n">
-        <v>797.59</v>
+        <v>1059.74</v>
       </c>
       <c r="E25" t="n">
-        <v>214.33</v>
+        <v>288.87</v>
       </c>
       <c r="F25" t="n">
-        <v>2229</v>
+        <v>1284</v>
       </c>
       <c r="G25" t="n">
-        <v>315503</v>
+        <v>397138</v>
       </c>
       <c r="H25" t="n">
-        <v>50000</v>
+        <v>66012</v>
       </c>
     </row>
     <row r="26">
@@ -1026,25 +1026,25 @@
         <v>45860</v>
       </c>
       <c r="B26" t="n">
-        <v>401.7</v>
+        <v>1405.35</v>
       </c>
       <c r="C26" t="n">
-        <v>6.68</v>
+        <v>24</v>
       </c>
       <c r="D26" t="n">
-        <v>292.31</v>
+        <v>1024.77</v>
       </c>
       <c r="E26" t="n">
-        <v>79.08</v>
+        <v>281.47</v>
       </c>
       <c r="F26" t="n">
-        <v>838</v>
+        <v>1186</v>
       </c>
       <c r="G26" t="n">
-        <v>110718</v>
+        <v>373103</v>
       </c>
       <c r="H26" t="n">
-        <v>19228</v>
+        <v>63361</v>
       </c>
     </row>
     <row r="27">
@@ -1052,25 +1052,25 @@
         <v>45861</v>
       </c>
       <c r="B27" t="n">
-        <v>1400.98</v>
+        <v>1016.42</v>
       </c>
       <c r="C27" t="n">
-        <v>21.82</v>
+        <v>16.47</v>
       </c>
       <c r="D27" t="n">
-        <v>1016.19</v>
+        <v>739.45</v>
       </c>
       <c r="E27" t="n">
-        <v>277.84</v>
+        <v>204.2</v>
       </c>
       <c r="F27" t="n">
-        <v>1946</v>
+        <v>1461</v>
       </c>
       <c r="G27" t="n">
-        <v>353471</v>
+        <v>291801</v>
       </c>
       <c r="H27" t="n">
-        <v>63112</v>
+        <v>45535</v>
       </c>
     </row>
     <row r="28">
@@ -1078,25 +1078,25 @@
         <v>45862</v>
       </c>
       <c r="B28" t="n">
-        <v>1086.84</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>17.85</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>791</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>214.28</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>2083</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>302651</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>46480</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1104,25 +1104,25 @@
         <v>45863</v>
       </c>
       <c r="B29" t="n">
-        <v>1030.85</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>18.03</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>742.9400000000001</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>210.85</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>1849</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>269127</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>47896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1130,25 +1130,25 @@
         <v>45864</v>
       </c>
       <c r="B30" t="n">
-        <v>1143.05</v>
+        <v>1484.73</v>
       </c>
       <c r="C30" t="n">
-        <v>19.16</v>
+        <v>24</v>
       </c>
       <c r="D30" t="n">
-        <v>827.8099999999999</v>
+        <v>1068.87</v>
       </c>
       <c r="E30" t="n">
-        <v>228.71</v>
+        <v>300.26</v>
       </c>
       <c r="F30" t="n">
-        <v>2323</v>
+        <v>1410</v>
       </c>
       <c r="G30" t="n">
-        <v>331221</v>
+        <v>393658</v>
       </c>
       <c r="H30" t="n">
-        <v>53155</v>
+        <v>64586</v>
       </c>
     </row>
     <row r="31">
@@ -1156,25 +1156,25 @@
         <v>45865</v>
       </c>
       <c r="B31" t="n">
-        <v>1569.43</v>
+        <v>1541.02</v>
       </c>
       <c r="C31" t="n">
         <v>24</v>
       </c>
       <c r="D31" t="n">
-        <v>1132.06</v>
+        <v>1115.28</v>
       </c>
       <c r="E31" t="n">
-        <v>311.51</v>
+        <v>302.67</v>
       </c>
       <c r="F31" t="n">
-        <v>2704</v>
+        <v>1513</v>
       </c>
       <c r="G31" t="n">
-        <v>387833</v>
+        <v>476564</v>
       </c>
       <c r="H31" t="n">
-        <v>66494</v>
+        <v>72485</v>
       </c>
     </row>
     <row r="32">
@@ -1182,25 +1182,25 @@
         <v>45866</v>
       </c>
       <c r="B32" t="n">
-        <v>1534.58</v>
+        <v>1535.33</v>
       </c>
       <c r="C32" t="n">
         <v>24</v>
       </c>
       <c r="D32" t="n">
-        <v>1117.58</v>
+        <v>1112.68</v>
       </c>
       <c r="E32" t="n">
-        <v>316.28</v>
+        <v>300.94</v>
       </c>
       <c r="F32" t="n">
-        <v>2120</v>
+        <v>1345</v>
       </c>
       <c r="G32" t="n">
-        <v>418283</v>
+        <v>399610</v>
       </c>
       <c r="H32" t="n">
-        <v>67324</v>
+        <v>70352</v>
       </c>
     </row>
     <row r="33">
@@ -1208,25 +1208,25 @@
         <v>45867</v>
       </c>
       <c r="B33" t="n">
-        <v>1425.94</v>
+        <v>1299.71</v>
       </c>
       <c r="C33" t="n">
-        <v>21.97</v>
+        <v>22.02</v>
       </c>
       <c r="D33" t="n">
-        <v>1038.57</v>
+        <v>947.33</v>
       </c>
       <c r="E33" t="n">
-        <v>284.51</v>
+        <v>264.58</v>
       </c>
       <c r="F33" t="n">
-        <v>2353</v>
+        <v>1214</v>
       </c>
       <c r="G33" t="n">
-        <v>370468</v>
+        <v>324536</v>
       </c>
       <c r="H33" t="n">
-        <v>60853</v>
+        <v>58548</v>
       </c>
     </row>
     <row r="34">
@@ -1234,25 +1234,25 @@
         <v>45868</v>
       </c>
       <c r="B34" t="n">
-        <v>314.8</v>
+        <v>1439.99</v>
       </c>
       <c r="C34" t="n">
-        <v>5.14</v>
+        <v>24</v>
       </c>
       <c r="D34" t="n">
-        <v>227.61</v>
+        <v>1044.79</v>
       </c>
       <c r="E34" t="n">
-        <v>63.24</v>
+        <v>290.78</v>
       </c>
       <c r="F34" t="n">
-        <v>613</v>
+        <v>1533</v>
       </c>
       <c r="G34" t="n">
-        <v>89554</v>
+        <v>407514</v>
       </c>
       <c r="H34" t="n">
-        <v>14220</v>
+        <v>66640</v>
       </c>
     </row>
     <row r="35">
@@ -1260,25 +1260,25 @@
         <v>45869</v>
       </c>
       <c r="B35" t="n">
-        <v>1326.13</v>
+        <v>951.4400000000001</v>
       </c>
       <c r="C35" t="n">
-        <v>20.26</v>
+        <v>14.79</v>
       </c>
       <c r="D35" t="n">
-        <v>963.5599999999999</v>
+        <v>691.1900000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>269.37</v>
+        <v>189.58</v>
       </c>
       <c r="F35" t="n">
-        <v>1892</v>
+        <v>1084</v>
       </c>
       <c r="G35" t="n">
-        <v>322681</v>
+        <v>239663</v>
       </c>
       <c r="H35" t="n">
-        <v>60447</v>
+        <v>42108</v>
       </c>
     </row>
     <row r="37">
@@ -1288,25 +1288,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>32763.09999999999</v>
+        <v>35813.19</v>
       </c>
       <c r="C37" t="n">
-        <v>526.74</v>
+        <v>580.4799999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>23725.68</v>
+        <v>25991.1</v>
       </c>
       <c r="E37" t="n">
-        <v>6528.05</v>
+        <v>7134.339999999999</v>
       </c>
       <c r="F37" t="n">
-        <v>54340</v>
+        <v>33133</v>
       </c>
       <c r="G37" t="n">
-        <v>8793979</v>
+        <v>9650794</v>
       </c>
       <c r="H37" t="n">
-        <v>1473538</v>
+        <v>1628939</v>
       </c>
     </row>
   </sheetData>

--- a/00-esmagadora-modelo/dados_sujos/apontamentos_mensais/producao_2025_07.xlsx
+++ b/00-esmagadora-modelo/dados_sujos/apontamentos_mensais/producao_2025_07.xlsx
@@ -480,25 +480,25 @@
         <v>45839</v>
       </c>
       <c r="B5" t="n">
-        <v>1546.8</v>
+        <v>1328.85</v>
       </c>
       <c r="C5" t="n">
-        <v>24</v>
+        <v>21.58</v>
       </c>
       <c r="D5" t="n">
-        <v>1122.11</v>
+        <v>955.38</v>
       </c>
       <c r="E5" t="n">
-        <v>303.6</v>
+        <v>262.65</v>
       </c>
       <c r="F5" t="n">
-        <v>1402</v>
+        <v>1367</v>
       </c>
       <c r="G5" t="n">
-        <v>408422</v>
+        <v>333357</v>
       </c>
       <c r="H5" t="n">
-        <v>67640</v>
+        <v>58354</v>
       </c>
     </row>
     <row r="6">
@@ -506,25 +506,25 @@
         <v>45840</v>
       </c>
       <c r="B6" t="n">
-        <v>1512.36</v>
+        <v>426.84</v>
       </c>
       <c r="C6" t="n">
-        <v>24</v>
+        <v>6.49</v>
       </c>
       <c r="D6" t="n">
-        <v>1097.55</v>
+        <v>309.88</v>
       </c>
       <c r="E6" t="n">
-        <v>302.07</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>1356</v>
+        <v>612</v>
       </c>
       <c r="G6" t="n">
-        <v>406068</v>
+        <v>120230</v>
       </c>
       <c r="H6" t="n">
-        <v>71541</v>
+        <v>20493</v>
       </c>
     </row>
     <row r="7">
@@ -532,25 +532,25 @@
         <v>45841</v>
       </c>
       <c r="B7" t="n">
-        <v>1481.83</v>
+        <v>664.42</v>
       </c>
       <c r="C7" t="n">
-        <v>23.76</v>
+        <v>10.74</v>
       </c>
       <c r="D7" t="n">
-        <v>1073.53</v>
+        <v>480.11</v>
       </c>
       <c r="E7" t="n">
-        <v>304.75</v>
+        <v>132.08</v>
       </c>
       <c r="F7" t="n">
-        <v>1195</v>
+        <v>645</v>
       </c>
       <c r="G7" t="n">
-        <v>397165</v>
+        <v>170219</v>
       </c>
       <c r="H7" t="n">
-        <v>70286</v>
+        <v>30528</v>
       </c>
     </row>
     <row r="8">
@@ -558,25 +558,25 @@
         <v>45842</v>
       </c>
       <c r="B8" t="n">
-        <v>1523.81</v>
+        <v>1521.34</v>
       </c>
       <c r="C8" t="n">
         <v>24</v>
       </c>
       <c r="D8" t="n">
-        <v>1111.17</v>
+        <v>1102.87</v>
       </c>
       <c r="E8" t="n">
-        <v>311.94</v>
+        <v>295.61</v>
       </c>
       <c r="F8" t="n">
-        <v>1446</v>
+        <v>1413</v>
       </c>
       <c r="G8" t="n">
-        <v>418025</v>
+        <v>401584</v>
       </c>
       <c r="H8" t="n">
-        <v>68819</v>
+        <v>71105</v>
       </c>
     </row>
     <row r="9">
@@ -584,25 +584,25 @@
         <v>45843</v>
       </c>
       <c r="B9" t="n">
-        <v>1372.55</v>
+        <v>1534.19</v>
       </c>
       <c r="C9" t="n">
-        <v>22.41</v>
+        <v>24</v>
       </c>
       <c r="D9" t="n">
-        <v>994.74</v>
+        <v>1108.79</v>
       </c>
       <c r="E9" t="n">
-        <v>264.67</v>
+        <v>319.5</v>
       </c>
       <c r="F9" t="n">
-        <v>1333</v>
+        <v>1397</v>
       </c>
       <c r="G9" t="n">
-        <v>366586</v>
+        <v>430630</v>
       </c>
       <c r="H9" t="n">
-        <v>57918</v>
+        <v>69416</v>
       </c>
     </row>
     <row r="10">
@@ -610,25 +610,25 @@
         <v>45844</v>
       </c>
       <c r="B10" t="n">
-        <v>1396.57</v>
+        <v>1367.15</v>
       </c>
       <c r="C10" t="n">
         <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>1014.2</v>
+        <v>992.87</v>
       </c>
       <c r="E10" t="n">
-        <v>280.11</v>
+        <v>274.61</v>
       </c>
       <c r="F10" t="n">
-        <v>1229</v>
+        <v>1244</v>
       </c>
       <c r="G10" t="n">
-        <v>350668</v>
+        <v>372073</v>
       </c>
       <c r="H10" t="n">
-        <v>65678</v>
+        <v>61895</v>
       </c>
     </row>
     <row r="11">
@@ -636,25 +636,25 @@
         <v>45845</v>
       </c>
       <c r="B11" t="n">
-        <v>1467.92</v>
+        <v>1487.22</v>
       </c>
       <c r="C11" t="n">
         <v>24</v>
       </c>
       <c r="D11" t="n">
-        <v>1066.16</v>
+        <v>1076.02</v>
       </c>
       <c r="E11" t="n">
-        <v>293.22</v>
+        <v>299.45</v>
       </c>
       <c r="F11" t="n">
-        <v>1271</v>
+        <v>1389</v>
       </c>
       <c r="G11" t="n">
-        <v>394570</v>
+        <v>396192</v>
       </c>
       <c r="H11" t="n">
-        <v>66589</v>
+        <v>69835</v>
       </c>
     </row>
     <row r="12">
@@ -662,25 +662,25 @@
         <v>45846</v>
       </c>
       <c r="B12" t="n">
-        <v>1520.73</v>
+        <v>1474.81</v>
       </c>
       <c r="C12" t="n">
         <v>24</v>
       </c>
       <c r="D12" t="n">
-        <v>1103.19</v>
+        <v>1066.12</v>
       </c>
       <c r="E12" t="n">
-        <v>304.07</v>
+        <v>287.09</v>
       </c>
       <c r="F12" t="n">
-        <v>1157</v>
+        <v>1150</v>
       </c>
       <c r="G12" t="n">
-        <v>381583</v>
+        <v>391232</v>
       </c>
       <c r="H12" t="n">
-        <v>67495</v>
+        <v>66209</v>
       </c>
     </row>
     <row r="13">
@@ -688,25 +688,25 @@
         <v>45847</v>
       </c>
       <c r="B13" t="n">
-        <v>1444.53</v>
+        <v>1549.3</v>
       </c>
       <c r="C13" t="n">
-        <v>23.01</v>
+        <v>24</v>
       </c>
       <c r="D13" t="n">
-        <v>1052.93</v>
+        <v>1114.77</v>
       </c>
       <c r="E13" t="n">
-        <v>281.58</v>
+        <v>302.9</v>
       </c>
       <c r="F13" t="n">
-        <v>1072</v>
+        <v>1383</v>
       </c>
       <c r="G13" t="n">
-        <v>373047</v>
+        <v>407200</v>
       </c>
       <c r="H13" t="n">
-        <v>65899</v>
+        <v>73158</v>
       </c>
     </row>
     <row r="14">
@@ -714,25 +714,25 @@
         <v>45848</v>
       </c>
       <c r="B14" t="n">
-        <v>1441.36</v>
+        <v>1420.03</v>
       </c>
       <c r="C14" t="n">
         <v>24</v>
       </c>
       <c r="D14" t="n">
-        <v>1042.4</v>
+        <v>1022.96</v>
       </c>
       <c r="E14" t="n">
-        <v>293.62</v>
+        <v>288.11</v>
       </c>
       <c r="F14" t="n">
-        <v>1421</v>
+        <v>1490</v>
       </c>
       <c r="G14" t="n">
-        <v>409746</v>
+        <v>361696</v>
       </c>
       <c r="H14" t="n">
-        <v>65398</v>
+        <v>64262</v>
       </c>
     </row>
     <row r="15">
@@ -740,25 +740,25 @@
         <v>45849</v>
       </c>
       <c r="B15" t="n">
-        <v>1232.29</v>
+        <v>762.17</v>
       </c>
       <c r="C15" t="n">
-        <v>20.31</v>
+        <v>12.98</v>
       </c>
       <c r="D15" t="n">
-        <v>899.27</v>
+        <v>553.6799999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>243.75</v>
+        <v>148.34</v>
       </c>
       <c r="F15" t="n">
-        <v>1122</v>
+        <v>762</v>
       </c>
       <c r="G15" t="n">
-        <v>323698</v>
+        <v>219829</v>
       </c>
       <c r="H15" t="n">
-        <v>53262</v>
+        <v>32709</v>
       </c>
     </row>
     <row r="16">
@@ -818,25 +818,25 @@
         <v>45852</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>1392.13</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>23.84</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>998.5599999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>274.19</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1372</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>373929</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>65678</v>
       </c>
     </row>
     <row r="19">
@@ -844,25 +844,25 @@
         <v>45853</v>
       </c>
       <c r="B19" t="n">
-        <v>1583.24</v>
+        <v>1344.41</v>
       </c>
       <c r="C19" t="n">
         <v>24</v>
       </c>
       <c r="D19" t="n">
-        <v>1146.11</v>
+        <v>973.41</v>
       </c>
       <c r="E19" t="n">
-        <v>312.84</v>
+        <v>263.87</v>
       </c>
       <c r="F19" t="n">
-        <v>1349</v>
+        <v>1302</v>
       </c>
       <c r="G19" t="n">
-        <v>415493</v>
+        <v>379195</v>
       </c>
       <c r="H19" t="n">
-        <v>74200</v>
+        <v>61275</v>
       </c>
     </row>
     <row r="20">
@@ -870,25 +870,25 @@
         <v>45854</v>
       </c>
       <c r="B20" t="n">
-        <v>1391.88</v>
+        <v>1476.85</v>
       </c>
       <c r="C20" t="n">
         <v>24</v>
       </c>
       <c r="D20" t="n">
-        <v>1005.57</v>
+        <v>1057.05</v>
       </c>
       <c r="E20" t="n">
-        <v>272.76</v>
+        <v>299.35</v>
       </c>
       <c r="F20" t="n">
-        <v>1171</v>
+        <v>1289</v>
       </c>
       <c r="G20" t="n">
-        <v>406169</v>
+        <v>379104</v>
       </c>
       <c r="H20" t="n">
-        <v>65138</v>
+        <v>63199</v>
       </c>
     </row>
     <row r="21">
@@ -896,25 +896,25 @@
         <v>45855</v>
       </c>
       <c r="B21" t="n">
-        <v>576.34</v>
+        <v>654.03</v>
       </c>
       <c r="C21" t="n">
-        <v>9.550000000000001</v>
+        <v>10.77</v>
       </c>
       <c r="D21" t="n">
-        <v>421.38</v>
+        <v>473.83</v>
       </c>
       <c r="E21" t="n">
-        <v>113.16</v>
+        <v>125.04</v>
       </c>
       <c r="F21" t="n">
-        <v>698</v>
+        <v>722</v>
       </c>
       <c r="G21" t="n">
-        <v>166979</v>
+        <v>178174</v>
       </c>
       <c r="H21" t="n">
-        <v>25243</v>
+        <v>30755</v>
       </c>
     </row>
     <row r="22">
@@ -922,25 +922,25 @@
         <v>45856</v>
       </c>
       <c r="B22" t="n">
-        <v>1486.02</v>
+        <v>1544.82</v>
       </c>
       <c r="C22" t="n">
         <v>24</v>
       </c>
       <c r="D22" t="n">
-        <v>1075.36</v>
+        <v>1122.09</v>
       </c>
       <c r="E22" t="n">
-        <v>304.01</v>
+        <v>302.9</v>
       </c>
       <c r="F22" t="n">
-        <v>1259</v>
+        <v>1453</v>
       </c>
       <c r="G22" t="n">
-        <v>421686</v>
+        <v>371215</v>
       </c>
       <c r="H22" t="n">
-        <v>69776</v>
+        <v>67411</v>
       </c>
     </row>
     <row r="23">
@@ -948,25 +948,25 @@
         <v>45857</v>
       </c>
       <c r="B23" t="n">
-        <v>1474.91</v>
+        <v>1451.16</v>
       </c>
       <c r="C23" t="n">
-        <v>24</v>
+        <v>23.51</v>
       </c>
       <c r="D23" t="n">
-        <v>1065.46</v>
+        <v>1047.85</v>
       </c>
       <c r="E23" t="n">
-        <v>283.22</v>
+        <v>282.64</v>
       </c>
       <c r="F23" t="n">
-        <v>1409</v>
+        <v>1307</v>
       </c>
       <c r="G23" t="n">
-        <v>400097</v>
+        <v>381843</v>
       </c>
       <c r="H23" t="n">
-        <v>65191</v>
+        <v>72885</v>
       </c>
     </row>
     <row r="24">
@@ -974,25 +974,25 @@
         <v>45858</v>
       </c>
       <c r="B24" t="n">
-        <v>1236.2</v>
+        <v>1488.89</v>
       </c>
       <c r="C24" t="n">
-        <v>20.16</v>
+        <v>24</v>
       </c>
       <c r="D24" t="n">
-        <v>895.87</v>
+        <v>1079</v>
       </c>
       <c r="E24" t="n">
-        <v>241.62</v>
+        <v>297.54</v>
       </c>
       <c r="F24" t="n">
-        <v>1213</v>
+        <v>1633</v>
       </c>
       <c r="G24" t="n">
-        <v>307205</v>
+        <v>414861</v>
       </c>
       <c r="H24" t="n">
-        <v>59239</v>
+        <v>73094</v>
       </c>
     </row>
     <row r="25">
@@ -1000,25 +1000,25 @@
         <v>45859</v>
       </c>
       <c r="B25" t="n">
-        <v>1449.86</v>
+        <v>1507.76</v>
       </c>
       <c r="C25" t="n">
         <v>24</v>
       </c>
       <c r="D25" t="n">
-        <v>1059.74</v>
+        <v>1096.88</v>
       </c>
       <c r="E25" t="n">
-        <v>288.87</v>
+        <v>306.33</v>
       </c>
       <c r="F25" t="n">
-        <v>1284</v>
+        <v>1184</v>
       </c>
       <c r="G25" t="n">
-        <v>397138</v>
+        <v>360950</v>
       </c>
       <c r="H25" t="n">
-        <v>66012</v>
+        <v>70756</v>
       </c>
     </row>
     <row r="26">
@@ -1026,25 +1026,25 @@
         <v>45860</v>
       </c>
       <c r="B26" t="n">
-        <v>1405.35</v>
+        <v>1505.87</v>
       </c>
       <c r="C26" t="n">
-        <v>24</v>
+        <v>23.64</v>
       </c>
       <c r="D26" t="n">
-        <v>1024.77</v>
+        <v>1096.6</v>
       </c>
       <c r="E26" t="n">
-        <v>281.47</v>
+        <v>293.54</v>
       </c>
       <c r="F26" t="n">
-        <v>1186</v>
+        <v>1499</v>
       </c>
       <c r="G26" t="n">
-        <v>373103</v>
+        <v>401375</v>
       </c>
       <c r="H26" t="n">
-        <v>63361</v>
+        <v>69757</v>
       </c>
     </row>
     <row r="27">
@@ -1052,25 +1052,25 @@
         <v>45861</v>
       </c>
       <c r="B27" t="n">
-        <v>1016.42</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>16.47</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>739.45</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>204.2</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>1461</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>291801</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>45535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1104,25 +1104,25 @@
         <v>45863</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>1462.37</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>23.71</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>1058.9</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>287.8</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>1433</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>390859</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>67583</v>
       </c>
     </row>
     <row r="30">
@@ -1130,25 +1130,25 @@
         <v>45864</v>
       </c>
       <c r="B30" t="n">
-        <v>1484.73</v>
+        <v>1331.78</v>
       </c>
       <c r="C30" t="n">
-        <v>24</v>
+        <v>22.26</v>
       </c>
       <c r="D30" t="n">
-        <v>1068.87</v>
+        <v>960.35</v>
       </c>
       <c r="E30" t="n">
-        <v>300.26</v>
+        <v>263.18</v>
       </c>
       <c r="F30" t="n">
-        <v>1410</v>
+        <v>1047</v>
       </c>
       <c r="G30" t="n">
-        <v>393658</v>
+        <v>363076</v>
       </c>
       <c r="H30" t="n">
-        <v>64586</v>
+        <v>60449</v>
       </c>
     </row>
     <row r="31">
@@ -1156,25 +1156,25 @@
         <v>45865</v>
       </c>
       <c r="B31" t="n">
-        <v>1541.02</v>
+        <v>1501.4</v>
       </c>
       <c r="C31" t="n">
         <v>24</v>
       </c>
       <c r="D31" t="n">
-        <v>1115.28</v>
+        <v>1088.84</v>
       </c>
       <c r="E31" t="n">
-        <v>302.67</v>
+        <v>298.16</v>
       </c>
       <c r="F31" t="n">
-        <v>1513</v>
+        <v>1233</v>
       </c>
       <c r="G31" t="n">
-        <v>476564</v>
+        <v>375226</v>
       </c>
       <c r="H31" t="n">
-        <v>72485</v>
+        <v>63591</v>
       </c>
     </row>
     <row r="32">
@@ -1182,25 +1182,25 @@
         <v>45866</v>
       </c>
       <c r="B32" t="n">
-        <v>1535.33</v>
+        <v>1422.8</v>
       </c>
       <c r="C32" t="n">
-        <v>24</v>
+        <v>22.89</v>
       </c>
       <c r="D32" t="n">
-        <v>1112.68</v>
+        <v>1035.23</v>
       </c>
       <c r="E32" t="n">
-        <v>300.94</v>
+        <v>287.24</v>
       </c>
       <c r="F32" t="n">
-        <v>1345</v>
+        <v>1396</v>
       </c>
       <c r="G32" t="n">
-        <v>399610</v>
+        <v>365513</v>
       </c>
       <c r="H32" t="n">
-        <v>70352</v>
+        <v>69175</v>
       </c>
     </row>
     <row r="33">
@@ -1208,25 +1208,25 @@
         <v>45867</v>
       </c>
       <c r="B33" t="n">
-        <v>1299.71</v>
+        <v>1472.78</v>
       </c>
       <c r="C33" t="n">
-        <v>22.02</v>
+        <v>21.98</v>
       </c>
       <c r="D33" t="n">
-        <v>947.33</v>
+        <v>1068.42</v>
       </c>
       <c r="E33" t="n">
-        <v>264.58</v>
+        <v>287.71</v>
       </c>
       <c r="F33" t="n">
-        <v>1214</v>
+        <v>1236</v>
       </c>
       <c r="G33" t="n">
-        <v>324536</v>
+        <v>358700</v>
       </c>
       <c r="H33" t="n">
-        <v>58548</v>
+        <v>64127</v>
       </c>
     </row>
     <row r="34">
@@ -1234,25 +1234,25 @@
         <v>45868</v>
       </c>
       <c r="B34" t="n">
-        <v>1439.99</v>
+        <v>1484.29</v>
       </c>
       <c r="C34" t="n">
         <v>24</v>
       </c>
       <c r="D34" t="n">
-        <v>1044.79</v>
+        <v>1073.58</v>
       </c>
       <c r="E34" t="n">
-        <v>290.78</v>
+        <v>291.75</v>
       </c>
       <c r="F34" t="n">
-        <v>1533</v>
+        <v>1278</v>
       </c>
       <c r="G34" t="n">
-        <v>407514</v>
+        <v>415309</v>
       </c>
       <c r="H34" t="n">
-        <v>66640</v>
+        <v>62604</v>
       </c>
     </row>
     <row r="35">
@@ -1260,25 +1260,25 @@
         <v>45869</v>
       </c>
       <c r="B35" t="n">
-        <v>951.4400000000001</v>
+        <v>1482.83</v>
       </c>
       <c r="C35" t="n">
-        <v>14.79</v>
+        <v>24</v>
       </c>
       <c r="D35" t="n">
-        <v>691.1900000000001</v>
+        <v>1068.27</v>
       </c>
       <c r="E35" t="n">
-        <v>189.58</v>
+        <v>286.71</v>
       </c>
       <c r="F35" t="n">
-        <v>1084</v>
+        <v>1572</v>
       </c>
       <c r="G35" t="n">
-        <v>239663</v>
+        <v>401689</v>
       </c>
       <c r="H35" t="n">
-        <v>42108</v>
+        <v>70879</v>
       </c>
     </row>
     <row r="37">
@@ -1288,25 +1288,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>35813.19</v>
+        <v>36060.49</v>
       </c>
       <c r="C37" t="n">
-        <v>580.4799999999999</v>
+        <v>584.39</v>
       </c>
       <c r="D37" t="n">
-        <v>25991.1</v>
+        <v>26082.31</v>
       </c>
       <c r="E37" t="n">
-        <v>7134.339999999999</v>
+        <v>7144.5</v>
       </c>
       <c r="F37" t="n">
-        <v>33133</v>
+        <v>33808</v>
       </c>
       <c r="G37" t="n">
-        <v>9650794</v>
+        <v>9515260</v>
       </c>
       <c r="H37" t="n">
-        <v>1628939</v>
+        <v>1651182</v>
       </c>
     </row>
   </sheetData>
